--- a/public/first-15/production-storyboard.xlsx
+++ b/public/first-15/production-storyboard.xlsx
@@ -441,7 +441,7 @@
     <t xml:space="preserve">If varAudioOn = True: one low sub-bass note at −26 LUFS, once, no tail. NO VOICE — the absence of a narrator is more serious than a narrator would be.</t>
   </si>
   <si>
-    <t xml:space="preserve">Modal. Continue → S3.5 micro-lesson (2 screens, ~40s) → return to S3.1 with varSafetyScore set to 60, btnDP1_C disabled, points capped at 15.</t>
+    <t xml:space="preserve">Modal. Continue → S3.5 micro-lesson (2 screens, ~40s) → return to S3.1 with varSafetyScore adjusted by the chosen option's authored cost (-20 here), clamped to 0-100, btnDP1_C disabled, points capped at 15.</t>
   </si>
   <si>
     <t xml:space="preserve">Three layer properties must be set EXPLICITLY because the defaults are wrong here: prevent the user from clicking the base layer; hide other slide layers; pause the base layer timeline. SET FOCUS TO THE LAYER ON SHOW — without it a keyboard user is still on the base layer behind a modal they cannot see. The accumulation-floor version of this layer is the SAME layer with a variable-swapped opening line; do not build two. Restore varSafetyScore to 60 at the end of the micro-lesson — above the floor of 55, well below the 80 threshold. Without the restore, re-deciding with option B lands at 50 and re-trips the floor forever.</t>
@@ -684,7 +684,7 @@
     <t xml:space="preserve">CRITICAL — remediation</t>
   </si>
   <si>
-    <t xml:space="preserve">Immediate critical layer. Under-inflated tires run hot; a hot tire on a loaded rear axle is how a blowout happens. Two-screen micro-lesson on heat, flex, and the rear axle, then a forced re-decide with Safety restored to 60 and this option disabled.</t>
+    <t xml:space="preserve">Immediate critical layer. Under-inflated tires run hot; a hot tire on a loaded rear axle is how a blowout happens. Two-screen micro-lesson on heat, flex, and the rear axle, then a forced re-decide with the option's authored Safety cost (-20) applied and this option disabled.</t>
   </si>
   <si>
     <t xml:space="preserve">D</t>
@@ -858,7 +858,7 @@
     <t xml:space="preserve">Remediation</t>
   </si>
   <si>
-    <t xml:space="preserve">Micro-lesson, Safety restored to 60, attempted option disabled with a rewritten label, re-decide capped at 15 points. varRemediationFlag is never reset.</t>
+    <t xml:space="preserve">Micro-lesson, the chosen option's authored Safety cost applied and clamped to 0-100, attempted option disabled with a rewritten label, re-decide capped at 15 points. varRemediationFlag is never reset.</t>
   </si>
   <si>
     <t xml:space="preserve">Variable</t>
@@ -1239,10 +1239,10 @@
     <t xml:space="preserve">Micro-lesson end</t>
   </si>
   <si>
-    <t xml:space="preserve">Set variable varSafetyScore = 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restore above the floor of 55 to prevent an infinite re-trap.</t>
+    <t xml:space="preserve">Adjust variable varSafetyScore - subtract the option's authored cost (20 at DP1, 25 at DP4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The flag guard, not a restore value, prevents the infinite re-trap: varRemediationFlag = True blocks the floor trigger for the rest of the attempt, so the score is free to stay low.</t>
   </si>
   <si>
     <t xml:space="preserve">Change state of btnDPn_&lt;critical option&gt; to Disabled</t>
@@ -1371,7 +1371,7 @@
     <t xml:space="preserve">After the micro-lesson the learner returns to the decision with Safety still at 50. Re-deciding DP1 with option B (−10) lands at 40, which trips the floor again — forever.</t>
   </si>
   <si>
-    <t xml:space="preserve">Two changes: restore varSafetyScore to 60 at the end of the micro-lesson (above the floor of 55, well below the 80 threshold), AND guard the floor trigger with varRemediationFlag = False so it fires at most once per attempt.</t>
+    <t xml:space="preserve">Two changes: apply the chosen option's authored Safety cost at the end of the micro-lesson and clamp to 0-100 - NOT a flat restore to 60. A flat restore hands points to any learner who reached the gate already below 60, so the gate rewards the violation it exists to punish; a gate that can raise your score is not a gate. AND guard the floor trigger with varRemediationFlag = False so it fires at most once per attempt. The guard is what prevents the re-trap, which is why the score no longer has to be propped up.</t>
   </si>
   <si>
     <t xml:space="preserve">A second attempt produces impossible scores.</t>
@@ -1446,7 +1446,7 @@
     <t xml:space="preserve">Floor fires at most once per attempt — re-deciding DP1 with option B after a restore does NOT re-trap</t>
   </si>
   <si>
-    <t xml:space="preserve">varSafetyScore restores to 60 after the micro-lesson, not 70</t>
+    <t xml:space="preserve">varSafetyScore moves by the option's authored cost after the micro-lesson - never upward</t>
   </si>
   <si>
     <t xml:space="preserve">Critical layer cannot be dismissed by clicking the base layer, or by Escape</t>

--- a/public/first-15/production-storyboard.xlsx
+++ b/public/first-15/production-storyboard.xlsx
@@ -1242,7 +1242,7 @@
     <t xml:space="preserve">Adjust variable varSafetyScore - subtract the option's authored cost (20 at DP1, 25 at DP4)</t>
   </si>
   <si>
-    <t xml:space="preserve">The flag guard, not a restore value, prevents the infinite re-trap: varRemediationFlag = True blocks the floor trigger for the rest of the attempt, so the score is free to stay low.</t>
+    <t xml:space="preserve">The guard, not a restore value, prevents the infinite re-trap: varFloorFired = True blocks the floor trigger for the rest of the attempt, so the score is free to stay low. Keep this separate from varRemediationFlag, which is the record and survives Retry - if one variable does both jobs, the floor never fires again after the first attempt.</t>
   </si>
   <si>
     <t xml:space="preserve">Change state of btnDPn_&lt;critical option&gt; to Disabled</t>
@@ -1371,7 +1371,7 @@
     <t xml:space="preserve">After the micro-lesson the learner returns to the decision with Safety still at 50. Re-deciding DP1 with option B (−10) lands at 40, which trips the floor again — forever.</t>
   </si>
   <si>
-    <t xml:space="preserve">Two changes: apply the chosen option's authored Safety cost at the end of the micro-lesson and clamp to 0-100 - NOT a flat restore to 60. A flat restore hands points to any learner who reached the gate already below 60, so the gate rewards the violation it exists to punish; a gate that can raise your score is not a gate. AND guard the floor trigger with varRemediationFlag = False so it fires at most once per attempt. The guard is what prevents the re-trap, which is why the score no longer has to be propped up.</t>
+    <t xml:space="preserve">Two changes: apply the chosen option's authored Safety cost at the end of the micro-lesson and clamp to 0-100 - NOT a flat restore to 60. A flat restore hands points to any learner who reached the gate already below 60, so the gate rewards the violation it exists to punish; a gate that can raise your score is not a gate. AND guard the floor trigger with varFloorFired = False so it fires at most once per attempt. The guard is what prevents the re-trap, which is why the score no longer has to be propped up. The categorical gate (1C, 4B) is NOT behind that guard - it is guarded per decision point, or a learner stopped once at DP1 walks into the dwelling at DP4 unchallenged.</t>
   </si>
   <si>
     <t xml:space="preserve">A second attempt produces impossible scores.</t>

--- a/public/first-15/production-storyboard.xlsx
+++ b/public/first-15/production-storyboard.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Client</t>
   </si>
   <si>
-    <t xml:space="preserve">MileOne Logistics — a realistic FICTIONAL organisation created for a portfolio project. No proprietary information or client data is used or implied. All operational specifics are illustrative and would require SME validation before a live release.</t>
+    <t xml:space="preserve">MileOne Logistics — a realistic FICTIONAL organization created for a portfolio project. No proprietary information or client data is used or implied. All operational specifics are illustrative and would require SME validation before a live release.</t>
   </si>
   <si>
     <t xml:space="preserve">Case study</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">[VAR] marks a variable reference rendered on screen. → marks navigation. Coordinates assume a 1280×720 stage with 64px margins. Type sizes are published values.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill colours</t>
+    <t xml:space="preserve">Fill colors</t>
   </si>
   <si>
     <t xml:space="preserve">Pale green = the preferred option. Pale red = a categorical critical choice that fires the safety interrupt unconditionally. Yellow = a cell for the developer to complete.</t>
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Narration</t>
   </si>
   <si>
-    <t xml:space="preserve">Interaction behaviour</t>
+    <t xml:space="preserve">Interaction behavior</t>
   </si>
   <si>
     <t xml:space="preserve">Developer notes</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">2 Dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">The interactive centre. Four information sources, free inspection order, enforced completeness. This is the screenshot that will represent the project.</t>
+    <t xml:space="preserve">The interactive center. Four information sources, free inspection order, enforced completeness. This is the screenshot that will represent the project.</t>
   </si>
   <si>
     <t xml:space="preserve">Ink ground. Header y=56: PRE-SHIFT REVIEW 13px uppercase Gold-light, then Route 214 · Station DC-3 · 7:10 a.m. 15px Silver. Subhead 18px Ivory y=92. Status bar x=920–1216 y=48: three stacked readouts, name 11px uppercase Silver, value mono 22px Ivory, 3px gold meter rule 96px beneath. Card grid 2×2 from x=64 y=176, each 544×212, 32px gutter, Graphite #2A2F37 with 1px #3A4048; 24px gold icon at 24,24; label 22px Ivory at 24,72; subtitle 15px Silver at 24,108; photo in the right 180px at 40% opacity with a left-edge fade. ROLL OUT x=1000–1216 y=628, Indigo fill / Graphite+lock when disabled.</t>
@@ -337,7 +337,7 @@
     <t xml:space="preserve">Card accessible names carry full meaning: 'Van 4412 — walkaround and gauges. One item needs a decision.' Never 'Card 1'. Visited conveyed by CHANGED SUBTITLE TEXT, not only the gold edge. Status values are live text so a screen reader says 'Safety 70'. Card photographs decorative. Disabled ROLL OUT must remain FOCUSABLE with the name 'Roll out — unavailable. Open all four review items first.' Focus order: header, 3 status readouts, cards 1–4, ROLL OUT.</t>
   </si>
   <si>
-    <t xml:space="preserve">The gate enforces a complete pre-shift review without an instruction telling the learner to look at everything — the interface teaches the behaviour. Inspection is free: looking costs no Time, because charging for looking would teach the wrong habit.</t>
+    <t xml:space="preserve">The gate enforces a complete pre-shift review without an instruction telling the learner to look at everything — the interface teaches the behavior. Inspection is free: looking costs no Time, because charging for looking would teach the wrong habit.</t>
   </si>
   <si>
     <t xml:space="preserve">SB-04</t>
@@ -372,7 +372,7 @@
     <t xml:space="preserve">varVanVisited is set on the HUB button, not here, so a learner arriving by any route still registers. Pressure values are live text, not an image — a client may localise units. KEEP YESTERDAY'S READING AT 16px and leave a build comment saying why; it will get 'tidied' into metadata otherwise, and the whole DP1 discrimination depends on it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tire photograph decorative. The rear-right row must announce as ONE unit — 'Rear right, 61, low, warning' — built as a single grouped object with a combined accessible name, not three announcements. Colour is never the only signal: crimson + triangle + the word LOW. Yesterday's reading must be in the focus order immediately after the four readings. Focus order: header, sub-line, section label, four readings, yesterday's reading, three condition lines, Back.</t>
+    <t xml:space="preserve">Tire photograph decorative. The rear-right row must announce as ONE unit — 'Rear right, 61, low, warning' — built as a single grouped object with a combined accessible name, not three announcements. Color is never the only signal: crimson + triangle + the word LOW. Yesterday's reading must be in the focus order immediately after the four readings. Focus order: header, sub-line, section label, four readings, yesterday's reading, three condition lines, Back.</t>
   </si>
   <si>
     <t xml:space="preserve">This screen is where the DP1 answer is EARNED. Two data points turn 'is 61 bad?' into 'is 61 getting worse?', which is the actual skill. Hiding yesterday's number would make the correct choice unguessable and the distractors unfair.</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">Trigger order on EVERY choice: adjust three dimension variables → adjust varPoints → set varDPnChoice and varDPnLabel → append varPathString → set varProgressStep → clamp Safety and Service to 0–100 → change meter states → critical check → navigate. Clamps are easy to omit and produce 'Safety 115' in the debrief. OPTION C FIRES lyrCriticalRisk UNCONDITIONALLY, not via the score floor; set varRemediationFlag = True AFTER the show trigger so the condition still evaluates. On revisit: btnDP1_C → Disabled with the label rewritten to 'Already tried — this one's a hard no'. Re-decide points cap at 15.</t>
   </si>
   <si>
-    <t xml:space="preserve">Each choice button's accessible name is the FULL option text, never 'Option A'. The persisting gauge plate is live text and sits in the focus order BEFORE the choices. Background photograph decorative — verify text contrast against the BLURRED plate, not the original image. Feedback copy references no colour and no position. Focus order: gauge plate, timestamp, body, question, choices A–D.</t>
+    <t xml:space="preserve">Each choice button's accessible name is the FULL option text, never 'Option A'. The persisting gauge plate is live text and sits in the focus order BEFORE the choices. Background photograph decorative — verify text contrast against the BLURRED plate, not the original image. Feedback copy references no color and no position. Focus order: gauge plate, timestamp, body, question, choices A–D.</t>
   </si>
   <si>
     <t xml:space="preserve">Safety comes first because precedence is taught by order, not assertion. The gauge plate persists so working memory is not what is assessed. Option D exists to make over-escalation costly — without it the learned lesson becomes 'escalate everything', which is the failure mode that gets safety training abandoned by week three.</t>
@@ -465,7 +465,7 @@
     <t xml:space="preserve">Assess LO3 and LO5 — protect commitments before absorbing volume, and renegotiate with a number.</t>
   </si>
   <si>
-    <t xml:space="preserve">Three constraint cards across the top x=64–1216 y=140, each 362×120, Graphite: label 13px uppercase Gold-light, constraint mono 20px Ivory, detail 14px Silver. TIMELINE y=320–400 x=64–1216: 1px #3A4048 baseline, hour ticks 07:00–18:00 in mono 13px Silver. Clinic window as a Gold #B8873B band 08:00–09:30, 24px tall, times as live text at both ends in Gold-light. 3px Indigo vertical marker at 10:20, visibly PAST the right edge of the band, labelled 'Current sequence arrives 10:20'. Live-text sentence directly beneath in 17px Ivory. Four choice cards from y=460.</t>
+    <t xml:space="preserve">Three constraint cards across the top x=64–1216 y=140, each 362×120, Graphite: label 13px uppercase Gold-light, constraint mono 20px Ivory, detail 14px Silver. TIMELINE y=320–400 x=64–1216: 1px #3A4048 baseline, hour ticks 07:00–18:00 in mono 13px Silver. Clinic window as a Gold #B8873B band 08:00–09:30, 24px tall, times as live text at both ends in Gold-light. 3px Indigo vertical marker at 10:20, visibly PAST the right edge of the band, labeled 'Current sequence arrives 10:20'. Live-text sentence directly beneath in 17px Ivory. Four choice cards from y=460.</t>
   </si>
   <si>
     <t xml:space="preserve">WINDOW 08:00–09:30 Ward 7 Dialysis Center, refrigerated tote 88-C | SIGNATURE Opens 09:00 Calloway &amp; Finch, stop 22 | VOLUME +18%, 2 associates out, 93 residential
@@ -487,7 +487,7 @@
     <t xml:space="preserve">Build the timeline as a GROUPED VECTOR OBJECT with the gold band and the indigo marker as separate named shapes, so the debrief can re-show it with the learner's actual outcome marker. Most reusable asset in the build. Option C costs 6 minutes and can drive varTimeRemaining negative — confirm the debrief renders negatives as 'Rolled out N minutes late', never 'TIME -2'. Every figure is live text, not baked into the graphic; a client will change these numbers.</t>
   </si>
   <si>
-    <t xml:space="preserve">THE SENTENCE BENEATH THE TIMELINE IS THE CONTENT; the timeline is enrichment. Highest-risk accessibility element in the build because its meaning is purely spatial — do not remove the sentence to tidy the layout. The gold band carries its times as text at both ends, so it is not distinguished by colour alone. Constraint cards pair label and value in one accessible name. Timeline graphic itself decorative. Focus order: 3 constraint cards, timeline sentence, Renata quote, question, choices A–D.</t>
+    <t xml:space="preserve">THE SENTENCE BENEATH THE TIMELINE IS THE CONTENT; the timeline is enrichment. Highest-risk accessibility element in the build because its meaning is purely spatial — do not remove the sentence to tidy the layout. The gold band carries its times as text at both ends, so it is not distinguished by color alone. Constraint cards pair label and value in one accessible name. Timeline graphic itself decorative. Focus order: 3 constraint cards, timeline sentence, Renata quote, question, choices A–D.</t>
   </si>
   <si>
     <t xml:space="preserve">The geometry makes an argument no copy could: the marker is visibly outside the band. No red arrows, no exclamation mark, no CONFLICT badge — and the restraint is what makes it look like a product rather than a course.</t>
@@ -531,7 +531,7 @@
     <t xml:space="preserve">The note's age and the note must be in the SAME live-text block, so the announcement is 'Account note, added 14 months ago: "Side gate code is 4412…"' — the age is half the lesson. Gate photograph decorative, accurately so: there is no information in it to describe, which is the design. Critical layer: focus set on show, Continue last. Focus order: timestamp, note block (age + text as one unit), the deciding-now line, question, choices.</t>
   </si>
   <si>
-    <t xml:space="preserve">Placing this decision in the bay rather than at the gate is the whole idea. A scenario at the gate would assess composure under pressure; this one assesses whether the learner uses the fifteen minutes they were given. The note's age rewards careful reading — exactly the behaviour the course wants.</t>
+    <t xml:space="preserve">Placing this decision in the bay rather than at the gate is the whole idea. A scenario at the gate would assess composure under pressure; this one assesses whether the learner uses the fifteen minutes they were given. The note's age rewards careful reading — exactly the behavior the course wants.</t>
   </si>
   <si>
     <t xml:space="preserve">SB-09</t>
@@ -1491,7 +1491,7 @@
     <t xml:space="preserve">Every number a decision depends on appears on screen as live text</t>
   </si>
   <si>
-    <t xml:space="preserve">No feedback copy references colour or position</t>
+    <t xml:space="preserve">No feedback copy references color or position</t>
   </si>
   <si>
     <t xml:space="preserve">No fabricated metric appears anywhere as a result</t>
@@ -1521,7 +1521,7 @@
     <t xml:space="preserve">Visual</t>
   </si>
   <si>
-    <t xml:space="preserve">Every colour pair measured, not eyeballed; gold never used as text on ivory</t>
+    <t xml:space="preserve">Every color pair measured, not eyeballed; gold never used as text on ivory</t>
   </si>
   <si>
     <t xml:space="preserve">All six states built on every interactive element</t>
@@ -1533,7 +1533,7 @@
     <t xml:space="preserve">Focus ring visible on charcoal, ivory, and indigo</t>
   </si>
   <si>
-    <t xml:space="preserve">No element relies on colour alone</t>
+    <t xml:space="preserve">No element relies on color alone</t>
   </si>
   <si>
     <t xml:space="preserve">Body text &gt;= 18px; display type &gt;= 28px</t>
